--- a/data_analysis/analysis_selected_solutions.xlsx
+++ b/data_analysis/analysis_selected_solutions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dados\Dafny\loopinv100_runs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dados\Dafny\TESTDAFNY110\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5EFA9D-AB7A-4C86-8EAF-0C06BECA54D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3729A8-E5A1-46D9-A5AE-A0FFDBED66FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{AD00872A-3429-4154-B9D8-B04F44A65181}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="323">
   <si>
     <t>Filename</t>
   </si>
@@ -1003,6 +1003,15 @@
   </si>
   <si>
     <t>LOC</t>
+  </si>
+  <si>
+    <t>Fibonacci_1_llm_simplified.dfy</t>
+  </si>
+  <si>
+    <t>task_id_566_1_llm_simplified.dfy</t>
+  </si>
+  <si>
+    <t>task_id_770_1_llm_simplified.dfy</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1076,21 +1085,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1107,10 +1111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1465,11 +1465,10 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
         <v>117</v>
       </c>
       <c r="E2">
@@ -1487,11 +1486,10 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
         <v>117</v>
       </c>
       <c r="E3">
@@ -1509,11 +1507,10 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
+      <c r="D4" t="s">
         <v>116</v>
       </c>
       <c r="E4">
@@ -1531,11 +1528,10 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6" t="s">
+      <c r="B5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
         <v>117</v>
       </c>
       <c r="E5">
@@ -1553,11 +1549,10 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" t="s">
         <v>318</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6" t="s">
+      <c r="D6" t="s">
         <v>318</v>
       </c>
       <c r="E6">
@@ -1575,11 +1570,10 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6" t="s">
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
         <v>117</v>
       </c>
       <c r="E7">
@@ -1597,11 +1591,10 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6" t="s">
+      <c r="D8" t="s">
         <v>115</v>
       </c>
       <c r="E8">
@@ -1619,11 +1612,10 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6" t="s">
+      <c r="D9" t="s">
         <v>116</v>
       </c>
       <c r="E9">
@@ -1641,11 +1633,10 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6" t="s">
+      <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" t="s">
         <v>117</v>
       </c>
       <c r="E10">
@@ -1663,11 +1654,10 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6" t="s">
+      <c r="D11" t="s">
         <v>115</v>
       </c>
       <c r="E11">
@@ -1685,11 +1675,10 @@
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6" t="s">
+      <c r="D12" t="s">
         <v>116</v>
       </c>
       <c r="E12">
@@ -1707,11 +1696,10 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6" t="s">
+      <c r="D13" t="s">
         <v>121</v>
       </c>
       <c r="E13">
@@ -1729,11 +1717,10 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6" t="s">
+      <c r="D14" t="s">
         <v>117</v>
       </c>
       <c r="E14">
@@ -1751,11 +1738,10 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6" t="s">
+      <c r="B15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" t="s">
         <v>117</v>
       </c>
       <c r="E15">
@@ -1773,11 +1759,10 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="s">
+      <c r="B16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" t="s">
         <v>117</v>
       </c>
       <c r="E16">
@@ -1795,11 +1780,10 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6" t="s">
+      <c r="D17" t="s">
         <v>121</v>
       </c>
       <c r="E17">
@@ -1817,11 +1801,10 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6" t="s">
+      <c r="D18" t="s">
         <v>318</v>
       </c>
       <c r="E18">
@@ -1839,11 +1822,11 @@
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6" t="s">
         <v>318</v>
       </c>
       <c r="E19">
@@ -1861,11 +1844,10 @@
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6" t="s">
+      <c r="D20" t="s">
         <v>117</v>
       </c>
       <c r="E20">
@@ -1880,14 +1862,13 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="6" t="s">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6" t="s">
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
         <v>117</v>
       </c>
       <c r="E21">
@@ -1905,11 +1886,10 @@
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6" t="s">
+      <c r="B22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" t="s">
         <v>117</v>
       </c>
       <c r="E22">
@@ -1927,11 +1907,10 @@
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6" t="s">
+      <c r="B23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
         <v>117</v>
       </c>
       <c r="E23">
@@ -1949,11 +1928,10 @@
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6" t="s">
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" t="s">
         <v>117</v>
       </c>
       <c r="E24">
@@ -1971,11 +1949,10 @@
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6" t="s">
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
         <v>117</v>
       </c>
       <c r="E25">
@@ -1993,11 +1970,10 @@
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6" t="s">
+      <c r="D26" t="s">
         <v>115</v>
       </c>
       <c r="E26">
@@ -2015,11 +1991,10 @@
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6" t="s">
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s">
         <v>117</v>
       </c>
       <c r="E27">
@@ -2037,11 +2012,10 @@
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6" t="s">
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
         <v>117</v>
       </c>
       <c r="E28">
@@ -2059,11 +2033,10 @@
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6" t="s">
+      <c r="B29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" t="s">
         <v>117</v>
       </c>
       <c r="E29">
@@ -2081,11 +2054,10 @@
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6" t="s">
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
         <v>117</v>
       </c>
       <c r="E30">
@@ -2103,11 +2075,10 @@
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6" t="s">
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
         <v>117</v>
       </c>
       <c r="E31">
@@ -2125,11 +2096,10 @@
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6" t="s">
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" t="s">
         <v>117</v>
       </c>
       <c r="E32">
@@ -2147,11 +2117,10 @@
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6" t="s">
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" t="s">
         <v>117</v>
       </c>
       <c r="E33">
@@ -2169,11 +2138,10 @@
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6" t="s">
+      <c r="B34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" t="s">
         <v>117</v>
       </c>
       <c r="E34">
@@ -2191,11 +2159,10 @@
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6" t="s">
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" t="s">
         <v>117</v>
       </c>
       <c r="E35">
@@ -2213,11 +2180,10 @@
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" t="s">
         <v>120</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6" t="s">
+      <c r="D36" t="s">
         <v>120</v>
       </c>
       <c r="E36">
@@ -2235,11 +2201,10 @@
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6" t="s">
+      <c r="D37" t="s">
         <v>119</v>
       </c>
       <c r="E37">
@@ -2257,11 +2222,10 @@
       <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6" t="s">
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" t="s">
         <v>117</v>
       </c>
       <c r="E38">
@@ -2279,11 +2243,10 @@
       <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6" t="s">
+      <c r="D39" t="s">
         <v>117</v>
       </c>
       <c r="E39">
@@ -2301,11 +2264,10 @@
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6" t="s">
+      <c r="D40" t="s">
         <v>116</v>
       </c>
       <c r="E40">
@@ -2323,11 +2285,10 @@
       <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6" t="s">
+      <c r="B41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" t="s">
         <v>117</v>
       </c>
       <c r="E41">
@@ -2345,11 +2306,10 @@
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6" t="s">
+      <c r="D42" t="s">
         <v>116</v>
       </c>
       <c r="E42">
@@ -2367,11 +2327,10 @@
       <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6" t="s">
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" t="s">
         <v>117</v>
       </c>
       <c r="E43">
@@ -2389,11 +2348,10 @@
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6" t="s">
+      <c r="B44" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" t="s">
         <v>117</v>
       </c>
       <c r="E44">
@@ -2411,11 +2369,10 @@
       <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" t="s">
         <v>119</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6" t="s">
+      <c r="D45" t="s">
         <v>115</v>
       </c>
       <c r="E45">
@@ -2433,11 +2390,10 @@
       <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6" t="s">
+      <c r="B46" t="s">
+        <v>117</v>
+      </c>
+      <c r="D46" t="s">
         <v>117</v>
       </c>
       <c r="E46">
@@ -2455,11 +2411,10 @@
       <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" t="s">
         <v>119</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6" t="s">
+      <c r="D47" t="s">
         <v>119</v>
       </c>
       <c r="E47">
@@ -2477,11 +2432,10 @@
       <c r="A48" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6" t="s">
+      <c r="B48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s">
         <v>117</v>
       </c>
       <c r="E48">
@@ -2499,11 +2453,10 @@
       <c r="A49" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" t="s">
         <v>115</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6" t="s">
+      <c r="D49" t="s">
         <v>115</v>
       </c>
       <c r="E49">
@@ -2521,11 +2474,10 @@
       <c r="A50" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6" t="s">
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" t="s">
         <v>117</v>
       </c>
       <c r="E50">
@@ -2543,11 +2495,10 @@
       <c r="A51" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" t="s">
         <v>115</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6" t="s">
+      <c r="D51" t="s">
         <v>115</v>
       </c>
       <c r="E51">
@@ -2565,11 +2516,10 @@
       <c r="A52" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6" t="s">
+      <c r="D52" t="s">
         <v>115</v>
       </c>
       <c r="E52">
@@ -2587,11 +2537,10 @@
       <c r="A53" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6" t="s">
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" t="s">
         <v>117</v>
       </c>
       <c r="E53">
@@ -2609,11 +2558,10 @@
       <c r="A54" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6" t="s">
+      <c r="D54" t="s">
         <v>116</v>
       </c>
       <c r="E54">
@@ -2631,11 +2579,10 @@
       <c r="A55" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6" t="s">
+      <c r="B55" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" t="s">
         <v>117</v>
       </c>
       <c r="E55">
@@ -2653,11 +2600,10 @@
       <c r="A56" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6" t="s">
+      <c r="B56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" t="s">
         <v>117</v>
       </c>
       <c r="E56">
@@ -2675,11 +2621,10 @@
       <c r="A57" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6" t="s">
+      <c r="B57" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57" t="s">
         <v>117</v>
       </c>
       <c r="E57">
@@ -2697,11 +2642,10 @@
       <c r="A58" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6" t="s">
+      <c r="D58" t="s">
         <v>121</v>
       </c>
       <c r="E58">
@@ -2719,11 +2663,10 @@
       <c r="A59" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6" t="s">
+      <c r="D59" t="s">
         <v>119</v>
       </c>
       <c r="E59">
@@ -2741,11 +2684,10 @@
       <c r="A60" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6" t="s">
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" t="s">
         <v>117</v>
       </c>
       <c r="E60">
@@ -2763,11 +2705,10 @@
       <c r="A61" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6" t="s">
+      <c r="B61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" t="s">
         <v>117</v>
       </c>
       <c r="E61">
@@ -2785,11 +2726,10 @@
       <c r="A62" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6" t="s">
+      <c r="B62" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62" t="s">
         <v>117</v>
       </c>
       <c r="E62">
@@ -2807,11 +2747,10 @@
       <c r="A63" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6" t="s">
+      <c r="D63" t="s">
         <v>122</v>
       </c>
       <c r="E63">
@@ -2829,11 +2768,10 @@
       <c r="A64" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6" t="s">
+      <c r="B64" t="s">
+        <v>117</v>
+      </c>
+      <c r="D64" t="s">
         <v>117</v>
       </c>
       <c r="E64">
@@ -2851,11 +2789,10 @@
       <c r="A65" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" t="s">
         <v>118</v>
       </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6" t="s">
+      <c r="D65" t="s">
         <v>118</v>
       </c>
       <c r="E65">
@@ -2873,11 +2810,10 @@
       <c r="A66" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6" t="s">
+      <c r="B66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" t="s">
         <v>117</v>
       </c>
       <c r="E66">
@@ -2895,11 +2831,10 @@
       <c r="A67" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" t="s">
         <v>119</v>
       </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6" t="s">
+      <c r="D67" t="s">
         <v>117</v>
       </c>
       <c r="E67">
@@ -2917,11 +2852,10 @@
       <c r="A68" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6" t="s">
+      <c r="B68" t="s">
+        <v>117</v>
+      </c>
+      <c r="D68" t="s">
         <v>117</v>
       </c>
       <c r="E68">
@@ -2939,11 +2873,10 @@
       <c r="A69" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" t="s">
         <v>119</v>
       </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6" t="s">
+      <c r="D69" t="s">
         <v>119</v>
       </c>
       <c r="E69">
@@ -2961,11 +2894,10 @@
       <c r="A70" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" t="s">
         <v>116</v>
       </c>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6" t="s">
+      <c r="D70" t="s">
         <v>116</v>
       </c>
       <c r="E70">
@@ -2983,11 +2915,10 @@
       <c r="A71" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6" t="s">
+      <c r="B71" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" t="s">
         <v>117</v>
       </c>
       <c r="E71">
@@ -3005,11 +2936,10 @@
       <c r="A72" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" t="s">
         <v>115</v>
       </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6" t="s">
+      <c r="D72" t="s">
         <v>115</v>
       </c>
       <c r="E72">
@@ -3027,11 +2957,10 @@
       <c r="A73" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6" t="s">
+      <c r="B73" t="s">
+        <v>117</v>
+      </c>
+      <c r="D73" t="s">
         <v>117</v>
       </c>
       <c r="E73">
@@ -3049,11 +2978,10 @@
       <c r="A74" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6" t="s">
+      <c r="B74" t="s">
+        <v>117</v>
+      </c>
+      <c r="D74" t="s">
         <v>117</v>
       </c>
       <c r="E74">
@@ -3071,11 +2999,10 @@
       <c r="A75" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6" t="s">
+      <c r="B75" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75" t="s">
         <v>117</v>
       </c>
       <c r="E75">
@@ -3093,11 +3020,10 @@
       <c r="A76" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6" t="s">
+      <c r="B76" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" t="s">
         <v>117</v>
       </c>
       <c r="E76">
@@ -3115,11 +3041,10 @@
       <c r="A77" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" t="s">
         <v>119</v>
       </c>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6" t="s">
+      <c r="D77" t="s">
         <v>119</v>
       </c>
       <c r="E77">
@@ -3137,11 +3062,10 @@
       <c r="A78" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" t="s">
         <v>115</v>
       </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6" t="s">
+      <c r="D78" t="s">
         <v>115</v>
       </c>
       <c r="E78">
@@ -3159,11 +3083,10 @@
       <c r="A79" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6" t="s">
+      <c r="B79" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" t="s">
         <v>117</v>
       </c>
       <c r="E79">
@@ -3181,11 +3104,10 @@
       <c r="A80" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" t="s">
         <v>118</v>
       </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6" t="s">
+      <c r="D80" t="s">
         <v>118</v>
       </c>
       <c r="E80">
@@ -3203,11 +3125,10 @@
       <c r="A81" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6" t="s">
+      <c r="B81" t="s">
+        <v>117</v>
+      </c>
+      <c r="D81" t="s">
         <v>117</v>
       </c>
       <c r="E81">
@@ -3225,11 +3146,10 @@
       <c r="A82" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6" t="s">
+      <c r="B82" t="s">
+        <v>117</v>
+      </c>
+      <c r="D82" t="s">
         <v>117</v>
       </c>
       <c r="E82">
@@ -3247,11 +3167,10 @@
       <c r="A83" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6" t="s">
+      <c r="B83" t="s">
+        <v>117</v>
+      </c>
+      <c r="D83" t="s">
         <v>117</v>
       </c>
       <c r="E83">
@@ -3269,11 +3188,10 @@
       <c r="A84" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6" t="s">
+      <c r="D84" t="s">
         <v>119</v>
       </c>
       <c r="E84">
@@ -3291,11 +3209,10 @@
       <c r="A85" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6" t="s">
+      <c r="B85" t="s">
+        <v>117</v>
+      </c>
+      <c r="D85" t="s">
         <v>117</v>
       </c>
       <c r="E85">
@@ -3313,11 +3230,10 @@
       <c r="A86" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6" t="s">
+      <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="D86" t="s">
         <v>117</v>
       </c>
       <c r="E86">
@@ -3335,11 +3251,10 @@
       <c r="A87" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6" t="s">
+      <c r="B87" t="s">
+        <v>117</v>
+      </c>
+      <c r="D87" t="s">
         <v>117</v>
       </c>
       <c r="E87">
@@ -3357,11 +3272,10 @@
       <c r="A88" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" t="s">
         <v>116</v>
       </c>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6" t="s">
+      <c r="D88" t="s">
         <v>116</v>
       </c>
       <c r="E88">
@@ -3379,11 +3293,10 @@
       <c r="A89" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6" t="s">
+      <c r="B89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D89" t="s">
         <v>117</v>
       </c>
       <c r="E89">
@@ -3401,11 +3314,10 @@
       <c r="A90" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6" t="s">
+      <c r="B90" t="s">
+        <v>117</v>
+      </c>
+      <c r="D90" t="s">
         <v>117</v>
       </c>
       <c r="E90">
@@ -3423,11 +3335,10 @@
       <c r="A91" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6" t="s">
+      <c r="B91" t="s">
+        <v>117</v>
+      </c>
+      <c r="D91" t="s">
         <v>117</v>
       </c>
       <c r="E91">
@@ -3445,11 +3356,10 @@
       <c r="A92" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" t="s">
         <v>116</v>
       </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6" t="s">
+      <c r="D92" t="s">
         <v>116</v>
       </c>
       <c r="E92">
@@ -3467,11 +3377,10 @@
       <c r="A93" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" t="s">
         <v>115</v>
       </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6" t="s">
+      <c r="D93" t="s">
         <v>115</v>
       </c>
       <c r="E93">
@@ -3489,11 +3398,10 @@
       <c r="A94" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6" t="s">
+      <c r="B94" t="s">
+        <v>117</v>
+      </c>
+      <c r="D94" t="s">
         <v>117</v>
       </c>
       <c r="E94">
@@ -3511,11 +3419,10 @@
       <c r="A95" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6" t="s">
+      <c r="B95" t="s">
+        <v>117</v>
+      </c>
+      <c r="D95" t="s">
         <v>117</v>
       </c>
       <c r="E95">
@@ -3533,11 +3440,10 @@
       <c r="A96" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6" t="s">
+      <c r="B96" t="s">
+        <v>117</v>
+      </c>
+      <c r="D96" t="s">
         <v>117</v>
       </c>
       <c r="E96">
@@ -3555,11 +3461,10 @@
       <c r="A97" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" t="s">
         <v>122</v>
       </c>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6" t="s">
+      <c r="D97" t="s">
         <v>122</v>
       </c>
       <c r="E97">
@@ -3577,11 +3482,10 @@
       <c r="A98" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6" t="s">
+      <c r="B98" t="s">
+        <v>117</v>
+      </c>
+      <c r="D98" t="s">
         <v>117</v>
       </c>
       <c r="E98">
@@ -3599,11 +3503,10 @@
       <c r="A99" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6" t="s">
+      <c r="B99" t="s">
+        <v>117</v>
+      </c>
+      <c r="D99" t="s">
         <v>117</v>
       </c>
       <c r="E99">
@@ -3621,11 +3524,10 @@
       <c r="A100" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" t="s">
         <v>116</v>
       </c>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6" t="s">
+      <c r="D100" t="s">
         <v>116</v>
       </c>
       <c r="E100">
@@ -3643,11 +3545,10 @@
       <c r="A101" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" t="s">
         <v>119</v>
       </c>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6" t="s">
+      <c r="D101" t="s">
         <v>119</v>
       </c>
       <c r="E101">
@@ -3665,11 +3566,10 @@
       <c r="A102" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6" t="s">
+      <c r="B102" t="s">
+        <v>117</v>
+      </c>
+      <c r="D102" t="s">
         <v>117</v>
       </c>
       <c r="E102">
@@ -3687,11 +3587,10 @@
       <c r="A103" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" t="s">
         <v>115</v>
       </c>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6" t="s">
+      <c r="D103" t="s">
         <v>115</v>
       </c>
       <c r="E103">
@@ -3709,11 +3608,10 @@
       <c r="A104" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6" t="s">
+      <c r="B104" t="s">
+        <v>117</v>
+      </c>
+      <c r="D104" t="s">
         <v>117</v>
       </c>
       <c r="E104">
@@ -3731,11 +3629,10 @@
       <c r="A105" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" t="s">
         <v>116</v>
       </c>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6" t="s">
+      <c r="D105" t="s">
         <v>116</v>
       </c>
       <c r="E105">
@@ -3753,11 +3650,10 @@
       <c r="A106" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6" t="s">
+      <c r="D106" t="s">
         <v>117</v>
       </c>
       <c r="E106">
@@ -3775,11 +3671,10 @@
       <c r="A107" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" t="s">
         <v>115</v>
       </c>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6" t="s">
+      <c r="D107" t="s">
         <v>115</v>
       </c>
       <c r="E107">
@@ -3797,11 +3692,10 @@
       <c r="A108" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6" t="s">
+      <c r="B108" t="s">
+        <v>117</v>
+      </c>
+      <c r="D108" t="s">
         <v>117</v>
       </c>
       <c r="E108">
@@ -3819,11 +3713,10 @@
       <c r="A109" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" t="s">
         <v>119</v>
       </c>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6" t="s">
+      <c r="D109" t="s">
         <v>119</v>
       </c>
       <c r="E109">
@@ -3841,11 +3734,10 @@
       <c r="A110" t="s">
         <v>123</v>
       </c>
-      <c r="B110" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6" t="s">
+      <c r="B110" t="s">
+        <v>117</v>
+      </c>
+      <c r="D110" t="s">
         <v>117</v>
       </c>
       <c r="E110">
@@ -3863,11 +3755,10 @@
       <c r="A111" t="s">
         <v>124</v>
       </c>
-      <c r="B111" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6" t="s">
+      <c r="B111" t="s">
+        <v>117</v>
+      </c>
+      <c r="D111" t="s">
         <v>117</v>
       </c>
       <c r="E111">
@@ -3889,15 +3780,15 @@
         <f>COUNTIF(B$2:B$111,A113)</f>
         <v>11</v>
       </c>
-      <c r="C113" s="9">
-        <f>B113/110</f>
+      <c r="C113" s="8">
+        <f t="shared" ref="C113:C122" si="3">B113/110</f>
         <v>0.1</v>
       </c>
-      <c r="D113" s="10">
-        <f>COUNTIF(D$2:D$111,A113)</f>
+      <c r="D113" s="3">
+        <f t="shared" ref="D113:D121" si="4">COUNTIF(D$2:D$111,A113)</f>
         <v>12</v>
       </c>
-      <c r="E113" s="9">
+      <c r="E113" s="8">
         <f>D113/110</f>
         <v>0.10909090909090909</v>
       </c>
@@ -3907,19 +3798,19 @@
         <v>116</v>
       </c>
       <c r="B114" s="3">
-        <f t="shared" ref="B114:B121" si="3">COUNTIF(B$2:B$111,A114)</f>
+        <f t="shared" ref="B114:B121" si="5">COUNTIF(B$2:B$111,A114)</f>
         <v>11</v>
       </c>
-      <c r="C114" s="9">
-        <f>B114/110</f>
+      <c r="C114" s="8">
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="D114" s="10">
-        <f>COUNTIF(D$2:D$111,A114)</f>
+      <c r="D114" s="3">
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E114" s="9">
-        <f t="shared" ref="E114:E121" si="4">D114/110</f>
+      <c r="E114" s="8">
+        <f t="shared" ref="E114:E121" si="6">D114/110</f>
         <v>0.1</v>
       </c>
     </row>
@@ -3928,19 +3819,19 @@
         <v>117</v>
       </c>
       <c r="B115" s="3">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+      <c r="C115" s="8">
         <f t="shared" si="3"/>
-        <v>63</v>
-      </c>
-      <c r="C115" s="9">
-        <f>B115/110</f>
         <v>0.57272727272727275</v>
       </c>
-      <c r="D115" s="10">
-        <f>COUNTIF(D$2:D$111,A115)</f>
+      <c r="D115" s="3">
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="E115" s="9">
-        <f t="shared" si="4"/>
+      <c r="E115" s="8">
+        <f t="shared" si="6"/>
         <v>0.61818181818181817</v>
       </c>
     </row>
@@ -3949,19 +3840,19 @@
         <v>119</v>
       </c>
       <c r="B116" s="3">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C116" s="8">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="C116" s="9">
-        <f>B116/110</f>
         <v>0.11818181818181818</v>
       </c>
-      <c r="D116" s="10">
-        <f>COUNTIF(D$2:D$111,A116)</f>
+      <c r="D116" s="3">
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="E116" s="9">
-        <f t="shared" si="4"/>
+      <c r="E116" s="8">
+        <f t="shared" si="6"/>
         <v>7.2727272727272724E-2</v>
       </c>
     </row>
@@ -3970,19 +3861,19 @@
         <v>118</v>
       </c>
       <c r="B117" s="3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="C117" s="8">
         <f t="shared" si="3"/>
+        <v>1.8181818181818181E-2</v>
+      </c>
+      <c r="D117" s="3">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="C117" s="9">
-        <f>B117/110</f>
-        <v>1.8181818181818181E-2</v>
-      </c>
-      <c r="D117" s="10">
-        <f>COUNTIF(D$2:D$111,A117)</f>
-        <v>2</v>
-      </c>
-      <c r="E117" s="9">
-        <f t="shared" si="4"/>
+      <c r="E117" s="8">
+        <f t="shared" si="6"/>
         <v>1.8181818181818181E-2</v>
       </c>
     </row>
@@ -3991,19 +3882,19 @@
         <v>122</v>
       </c>
       <c r="B118" s="3">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="C118" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="C118" s="9">
-        <f>B118/110</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D118" s="10">
-        <f>COUNTIF(D$2:D$111,A118)</f>
+      <c r="D118" s="3">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E118" s="9">
-        <f t="shared" si="4"/>
+      <c r="E118" s="8">
+        <f t="shared" si="6"/>
         <v>1.8181818181818181E-2</v>
       </c>
     </row>
@@ -4012,19 +3903,19 @@
         <v>318</v>
       </c>
       <c r="B119" s="3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="C119" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="C119" s="9">
-        <f>B119/110</f>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="D119" s="10">
-        <f>COUNTIF(D$2:D$111,A119)</f>
+      <c r="D119" s="3">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="E119" s="9">
-        <f t="shared" si="4"/>
+      <c r="E119" s="8">
+        <f t="shared" si="6"/>
         <v>2.7272727272727271E-2</v>
       </c>
     </row>
@@ -4033,19 +3924,19 @@
         <v>121</v>
       </c>
       <c r="B120" s="3">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="C120" s="8">
         <f t="shared" si="3"/>
+        <v>2.7272727272727271E-2</v>
+      </c>
+      <c r="D120" s="3">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="C120" s="9">
-        <f>B120/110</f>
-        <v>2.7272727272727271E-2</v>
-      </c>
-      <c r="D120" s="10">
-        <f>COUNTIF(D$2:D$111,A120)</f>
-        <v>3</v>
-      </c>
-      <c r="E120" s="9">
-        <f t="shared" si="4"/>
+      <c r="E120" s="8">
+        <f t="shared" si="6"/>
         <v>2.7272727272727271E-2</v>
       </c>
     </row>
@@ -4054,19 +3945,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="C121" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="C121" s="9">
-        <f>B121/110</f>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="D121" s="10">
-        <f>COUNTIF(D$2:D$111,A121)</f>
+      <c r="D121" s="3">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="E121" s="9">
-        <f t="shared" si="4"/>
+      <c r="E121" s="8">
+        <f t="shared" si="6"/>
         <v>9.0909090909090905E-3</v>
       </c>
     </row>
@@ -4074,19 +3965,19 @@
       <c r="A122" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="7">
         <f>SUM(B113:B121)</f>
         <v>110</v>
       </c>
-      <c r="C122" s="11">
-        <f>B122/110</f>
+      <c r="C122" s="9">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="7">
         <f>SUM(D113:D121)</f>
         <v>110</v>
       </c>
-      <c r="E122" s="11">
+      <c r="E122" s="9">
         <f>D122/110</f>
         <v>1</v>
       </c>
@@ -4113,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92188F1E-D925-46B9-ADC7-C28E799D076F}">
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28.73046875" customWidth="1"/>
@@ -4623,11 +4514,11 @@
       </c>
       <c r="G16">
         <f>IFERROR(VLOOKUP(C16,locs_minimized!A:B,2,0),F16)</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I16">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
@@ -4687,11 +4578,11 @@
       </c>
       <c r="G18">
         <f>IFERROR(VLOOKUP(C18,locs_minimized!A:B,2,0),F18)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I18">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -4815,11 +4706,11 @@
       </c>
       <c r="G22">
         <f>IFERROR(VLOOKUP(C22,locs_minimized!A:B,2,0),F22)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I22">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -5007,11 +4898,11 @@
       </c>
       <c r="G28">
         <f>IFERROR(VLOOKUP(C28,locs_minimized!A:B,2,0),F28)</f>
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I28">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -5167,11 +5058,11 @@
       </c>
       <c r="G33">
         <f>IFERROR(VLOOKUP(C33,locs_minimized!A:B,2,0),F33)</f>
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I33">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -5615,11 +5506,11 @@
       </c>
       <c r="G47">
         <f>IFERROR(VLOOKUP(C47,locs_minimized!A:B,2,0),F47)</f>
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I47">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -5775,11 +5666,11 @@
       </c>
       <c r="G52">
         <f>IFERROR(VLOOKUP(C52,locs_minimized!A:B,2,0),F52)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I52">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
@@ -6255,11 +6146,11 @@
       </c>
       <c r="G67">
         <f>IFERROR(VLOOKUP(C67,locs_minimized!A:B,2,0),F67)</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I67">
         <f t="shared" ref="I67:I110" si="3">G67-D67</f>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
@@ -6799,11 +6690,11 @@
       </c>
       <c r="G84">
         <f>IFERROR(VLOOKUP(C84,locs_minimized!A:B,2,0),F84)</f>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I84">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -6991,11 +6882,11 @@
       </c>
       <c r="G90">
         <f>IFERROR(VLOOKUP(C90,locs_minimized!A:B,2,0),F90)</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I90">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -7439,11 +7330,11 @@
       </c>
       <c r="G104">
         <f>IFERROR(VLOOKUP(C104,locs_minimized!A:B,2,0),F104)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I104">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.45">
@@ -7503,11 +7394,11 @@
       </c>
       <c r="G106">
         <f>IFERROR(VLOOKUP(C106,locs_minimized!A:B,2,0),F106)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I106">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -7624,11 +7515,11 @@
       </c>
       <c r="G110">
         <f t="shared" si="4"/>
-        <v>3820</v>
+        <v>3809</v>
       </c>
       <c r="I110">
         <f t="shared" si="3"/>
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -7641,7 +7532,13 @@
       </c>
       <c r="G111" s="5">
         <f>G110/D110-1</f>
-        <v>0.12452163673829841</v>
+        <v>0.12128348542831913</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G112">
+        <f>(G110-E110)/(F110-E110)</f>
+        <v>0.44090177133655395</v>
       </c>
     </row>
   </sheetData>
@@ -7655,18 +7552,18 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="1" t="s">
         <v>234</v>
       </c>
     </row>
@@ -7674,10 +7571,10 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>38</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2">
         <v>30</v>
       </c>
     </row>
@@ -7685,10 +7582,10 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>44</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3">
         <v>26</v>
       </c>
     </row>
@@ -7696,10 +7593,10 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>28</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4">
         <v>23</v>
       </c>
     </row>
@@ -7707,10 +7604,10 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>38</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5">
         <v>28</v>
       </c>
     </row>
@@ -7718,10 +7615,10 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>41</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>23</v>
       </c>
     </row>
@@ -7729,10 +7626,10 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>18</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>15</v>
       </c>
     </row>
@@ -7740,10 +7637,10 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>21</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8">
         <v>16</v>
       </c>
     </row>
@@ -7751,10 +7648,10 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>38</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9">
         <v>22</v>
       </c>
     </row>
@@ -7762,10 +7659,10 @@
       <c r="A10" t="s">
         <v>235</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>104</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10">
         <v>49</v>
       </c>
     </row>
@@ -7773,10 +7670,10 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <v>25</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11">
         <v>20</v>
       </c>
     </row>
@@ -7784,10 +7681,10 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12">
         <v>29</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12">
         <v>23</v>
       </c>
     </row>
@@ -7795,10 +7692,10 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13">
         <v>57</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13">
         <v>27</v>
       </c>
     </row>
@@ -7806,10 +7703,10 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14">
         <v>40</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14">
         <v>23</v>
       </c>
     </row>
@@ -7817,10 +7714,10 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15">
         <v>23</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15">
         <v>19</v>
       </c>
     </row>
@@ -7828,10 +7725,10 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16">
         <v>20</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16">
         <v>14</v>
       </c>
     </row>
@@ -7839,10 +7736,10 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17">
         <v>45</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17">
         <v>26</v>
       </c>
     </row>
@@ -7850,10 +7747,10 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18">
         <v>39</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18">
         <v>28</v>
       </c>
     </row>
@@ -7861,10 +7758,10 @@
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19">
         <v>46</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19">
         <v>26</v>
       </c>
     </row>
@@ -7872,10 +7769,10 @@
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20">
         <v>46</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20">
         <v>25</v>
       </c>
     </row>
@@ -7883,10 +7780,10 @@
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21">
         <v>30</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21">
         <v>23</v>
       </c>
     </row>
@@ -7894,10 +7791,10 @@
       <c r="A22" t="s">
         <v>236</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22">
         <v>227</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22">
         <v>20</v>
       </c>
     </row>
@@ -7905,10 +7802,10 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23">
         <v>48</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23">
         <v>17</v>
       </c>
     </row>
@@ -7916,10 +7813,10 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24">
         <v>57</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24">
         <v>47</v>
       </c>
     </row>
@@ -7927,10 +7824,10 @@
       <c r="A25" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25">
         <v>19</v>
       </c>
     </row>
@@ -7938,10 +7835,10 @@
       <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26">
         <v>38</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26">
         <v>26</v>
       </c>
     </row>
@@ -7949,10 +7846,10 @@
       <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27">
         <v>26</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27">
         <v>21</v>
       </c>
     </row>
@@ -7960,10 +7857,10 @@
       <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28">
         <v>24</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28">
         <v>22</v>
       </c>
     </row>
@@ -7971,10 +7868,10 @@
       <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29">
         <v>30</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29">
         <v>27</v>
       </c>
     </row>
@@ -7982,10 +7879,10 @@
       <c r="A30" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30">
         <v>46</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30">
         <v>23</v>
       </c>
     </row>
@@ -7993,10 +7890,10 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31">
         <v>28</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31">
         <v>18</v>
       </c>
     </row>
@@ -8004,10 +7901,10 @@
       <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32">
         <v>37</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32">
         <v>25</v>
       </c>
     </row>
@@ -8015,10 +7912,10 @@
       <c r="A33" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33">
         <v>59</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33">
         <f>33-8</f>
         <v>25</v>
       </c>
@@ -8027,10 +7924,10 @@
       <c r="A34" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34">
         <v>28</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34">
         <v>21</v>
       </c>
     </row>
@@ -8038,10 +7935,10 @@
       <c r="A35" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35">
         <v>30</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35">
         <v>16</v>
       </c>
     </row>
@@ -8049,10 +7946,10 @@
       <c r="A36" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36">
         <v>33</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36">
         <v>24</v>
       </c>
     </row>
@@ -8060,10 +7957,10 @@
       <c r="A37" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37">
         <v>26</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37">
         <v>21</v>
       </c>
     </row>
@@ -8071,10 +7968,10 @@
       <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38">
         <v>37</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38">
         <v>21</v>
       </c>
     </row>
@@ -8082,10 +7979,10 @@
       <c r="A39" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39">
         <v>20</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39">
         <v>14</v>
       </c>
     </row>
@@ -8093,10 +7990,10 @@
       <c r="A40" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40">
         <v>28</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40">
         <v>22</v>
       </c>
     </row>
@@ -8104,10 +8001,10 @@
       <c r="A41" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41">
         <v>21</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41">
         <v>18</v>
       </c>
     </row>
@@ -8115,10 +8012,10 @@
       <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42">
         <v>27</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42">
         <v>22</v>
       </c>
     </row>
@@ -8126,10 +8023,10 @@
       <c r="A43" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43">
         <v>26</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43">
         <v>22</v>
       </c>
     </row>
@@ -8137,10 +8034,10 @@
       <c r="A44" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44">
         <v>25</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44">
         <v>22</v>
       </c>
     </row>
@@ -8148,10 +8045,10 @@
       <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45">
         <v>24</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45">
         <v>19</v>
       </c>
     </row>
@@ -8159,10 +8056,10 @@
       <c r="A46" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46">
         <v>23</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46">
         <v>18</v>
       </c>
     </row>
@@ -8170,10 +8067,10 @@
       <c r="A47" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47">
         <v>21</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47">
         <v>19</v>
       </c>
     </row>
@@ -8181,10 +8078,10 @@
       <c r="A48" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48">
         <v>19</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48">
         <v>14</v>
       </c>
     </row>
@@ -8192,10 +8089,10 @@
       <c r="A49" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49">
         <v>42</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49">
         <v>23</v>
       </c>
     </row>
@@ -8203,10 +8100,10 @@
       <c r="A50" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50">
         <v>28</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50">
         <v>25</v>
       </c>
     </row>
@@ -8214,10 +8111,10 @@
       <c r="A51" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51">
         <v>29</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51">
         <v>24</v>
       </c>
     </row>
@@ -8225,10 +8122,10 @@
       <c r="A52" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52">
         <v>33</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52">
         <v>24</v>
       </c>
     </row>
@@ -8236,10 +8133,10 @@
       <c r="A53" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53">
         <v>37</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53">
         <v>28</v>
       </c>
     </row>
@@ -8247,10 +8144,10 @@
       <c r="A54" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54">
         <v>20</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54">
         <v>17</v>
       </c>
     </row>
@@ -8258,10 +8155,10 @@
       <c r="A55" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55">
         <v>30</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55">
         <v>21</v>
       </c>
     </row>
@@ -8269,10 +8166,10 @@
       <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56">
         <v>19</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56">
         <v>14</v>
       </c>
     </row>
@@ -8280,10 +8177,10 @@
       <c r="A57" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57">
         <v>26</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57">
         <v>19</v>
       </c>
     </row>
@@ -8291,10 +8188,10 @@
       <c r="A58" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58">
         <v>23</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58">
         <v>21</v>
       </c>
     </row>
@@ -8302,10 +8199,10 @@
       <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59">
         <v>26</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59">
         <v>21</v>
       </c>
     </row>
@@ -8313,10 +8210,10 @@
       <c r="A60" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B60">
         <v>23</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60">
         <v>18</v>
       </c>
     </row>
@@ -8324,10 +8221,10 @@
       <c r="A61" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61">
         <v>34</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61">
         <v>30</v>
       </c>
     </row>
@@ -8335,10 +8232,10 @@
       <c r="A62" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B62">
         <v>26</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62">
         <v>21</v>
       </c>
     </row>
@@ -8346,10 +8243,10 @@
       <c r="A63" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63">
         <v>54</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63">
         <v>26</v>
       </c>
     </row>
@@ -8357,10 +8254,10 @@
       <c r="A64" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B64">
         <v>27</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64">
         <v>22</v>
       </c>
     </row>
@@ -8368,10 +8265,10 @@
       <c r="A65" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65">
         <v>43</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65">
         <v>36</v>
       </c>
     </row>
@@ -8379,10 +8276,10 @@
       <c r="A66" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66">
         <v>24</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66">
         <v>19</v>
       </c>
     </row>
@@ -8390,10 +8287,10 @@
       <c r="A67" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67">
         <v>28</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67">
         <v>22</v>
       </c>
     </row>
@@ -8401,10 +8298,10 @@
       <c r="A68" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B68">
         <v>23</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68">
         <v>20</v>
       </c>
     </row>
@@ -8412,10 +8309,10 @@
       <c r="A69" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B69">
         <v>37</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69">
         <v>18</v>
       </c>
     </row>
@@ -8423,10 +8320,10 @@
       <c r="A70" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="6">
+      <c r="B70">
         <v>56</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70">
         <v>20</v>
       </c>
     </row>
@@ -8434,10 +8331,10 @@
       <c r="A71" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71">
         <v>34</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71">
         <v>27</v>
       </c>
     </row>
@@ -8445,10 +8342,10 @@
       <c r="A72" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B72">
         <v>23</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72">
         <v>15</v>
       </c>
     </row>
@@ -8456,10 +8353,10 @@
       <c r="A73" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B73">
         <v>49</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73">
         <v>42</v>
       </c>
     </row>
@@ -8467,10 +8364,10 @@
       <c r="A74" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="6">
+      <c r="B74">
         <v>15</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74">
         <v>13</v>
       </c>
     </row>
@@ -8478,10 +8375,10 @@
       <c r="A75" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B75">
         <v>48</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75">
         <v>37</v>
       </c>
     </row>
@@ -8489,10 +8386,10 @@
       <c r="A76" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="6">
+      <c r="B76">
         <v>21</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76">
         <v>17</v>
       </c>
     </row>
@@ -8500,10 +8397,10 @@
       <c r="A77" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B77">
         <v>31</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77">
         <v>25</v>
       </c>
     </row>
@@ -8511,10 +8408,10 @@
       <c r="A78" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="6">
+      <c r="B78">
         <v>22</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78">
         <v>18</v>
       </c>
     </row>
@@ -8522,10 +8419,10 @@
       <c r="A79" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79">
         <v>26</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79">
         <v>21</v>
       </c>
     </row>
@@ -8533,10 +8430,10 @@
       <c r="A80" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="6">
+      <c r="B80">
         <v>24</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80">
         <v>18</v>
       </c>
     </row>
@@ -8544,10 +8441,10 @@
       <c r="A81" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81">
         <v>30</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81">
         <v>21</v>
       </c>
     </row>
@@ -8555,10 +8452,10 @@
       <c r="A82" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="6">
+      <c r="B82">
         <v>25</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82">
         <v>20</v>
       </c>
     </row>
@@ -8566,10 +8463,10 @@
       <c r="A83" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83">
         <v>22</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83">
         <v>17</v>
       </c>
     </row>
@@ -8577,10 +8474,10 @@
       <c r="A84" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="6">
+      <c r="B84">
         <v>36</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84">
         <v>24</v>
       </c>
     </row>
@@ -8588,10 +8485,10 @@
       <c r="A85" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85">
         <v>49</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85">
         <v>30</v>
       </c>
     </row>
@@ -8599,10 +8496,10 @@
       <c r="A86" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="6">
+      <c r="B86">
         <v>48</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86">
         <v>22</v>
       </c>
     </row>
@@ -8610,10 +8507,10 @@
       <c r="A87" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87">
         <v>31</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87">
         <v>25</v>
       </c>
     </row>
@@ -8621,10 +8518,10 @@
       <c r="A88" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B88">
         <v>27</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88">
         <v>25</v>
       </c>
     </row>
@@ -8632,10 +8529,10 @@
       <c r="A89" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89">
         <v>28</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89">
         <v>25</v>
       </c>
     </row>
@@ -8643,10 +8540,10 @@
       <c r="A90" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="6">
+      <c r="B90">
         <v>23</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90">
         <v>18</v>
       </c>
     </row>
@@ -8654,10 +8551,10 @@
       <c r="A91" t="s">
         <v>89</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91">
         <v>24</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91">
         <v>19</v>
       </c>
     </row>
@@ -8665,10 +8562,10 @@
       <c r="A92" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="6">
+      <c r="B92">
         <v>28</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92">
         <v>23</v>
       </c>
     </row>
@@ -8676,10 +8573,10 @@
       <c r="A93" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93">
         <v>24</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93">
         <v>21</v>
       </c>
     </row>
@@ -8687,10 +8584,10 @@
       <c r="A94" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="6">
+      <c r="B94">
         <v>22</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94">
         <v>18</v>
       </c>
     </row>
@@ -8698,10 +8595,10 @@
       <c r="A95" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95">
         <v>31</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95">
         <v>28</v>
       </c>
     </row>
@@ -8709,10 +8606,10 @@
       <c r="A96" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="6">
+      <c r="B96">
         <v>38</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96">
         <v>28</v>
       </c>
     </row>
@@ -8720,10 +8617,10 @@
       <c r="A97" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97">
         <v>28</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97">
         <v>25</v>
       </c>
     </row>
@@ -8731,10 +8628,10 @@
       <c r="A98" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="6">
+      <c r="B98">
         <v>33</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98">
         <v>24</v>
       </c>
     </row>
@@ -8742,10 +8639,10 @@
       <c r="A99" t="s">
         <v>97</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99">
         <v>23</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99">
         <v>20</v>
       </c>
     </row>
@@ -8753,10 +8650,10 @@
       <c r="A100" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="6">
+      <c r="B100">
         <v>24</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100">
         <v>21</v>
       </c>
     </row>
@@ -8764,10 +8661,10 @@
       <c r="A101" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B101">
         <v>57</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101">
         <v>36</v>
       </c>
     </row>
@@ -8775,10 +8672,10 @@
       <c r="A102" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="6">
+      <c r="B102">
         <v>28</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102">
         <v>26</v>
       </c>
     </row>
@@ -8786,10 +8683,10 @@
       <c r="A103" t="s">
         <v>101</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103">
         <v>30</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103">
         <v>23</v>
       </c>
     </row>
@@ -8797,10 +8694,10 @@
       <c r="A104" t="s">
         <v>102</v>
       </c>
-      <c r="B104" s="6">
+      <c r="B104">
         <v>35</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104">
         <v>26</v>
       </c>
     </row>
@@ -8808,10 +8705,10 @@
       <c r="A105" t="s">
         <v>103</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105">
         <v>22</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105">
         <v>19</v>
       </c>
     </row>
@@ -8819,10 +8716,10 @@
       <c r="A106" t="s">
         <v>104</v>
       </c>
-      <c r="B106" s="6">
+      <c r="B106">
         <v>30</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106">
         <v>17</v>
       </c>
     </row>
@@ -8830,10 +8727,10 @@
       <c r="A107" t="s">
         <v>105</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107">
         <v>29</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107">
         <v>26</v>
       </c>
     </row>
@@ -8841,10 +8738,10 @@
       <c r="A108" t="s">
         <v>106</v>
       </c>
-      <c r="B108" s="6">
+      <c r="B108">
         <v>35</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108">
         <v>24</v>
       </c>
     </row>
@@ -8852,10 +8749,10 @@
       <c r="A109" t="s">
         <v>107</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B109">
         <v>24</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109">
         <v>22</v>
       </c>
     </row>
@@ -8863,10 +8760,10 @@
       <c r="A110" t="s">
         <v>108</v>
       </c>
-      <c r="B110" s="6">
+      <c r="B110">
         <v>29</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110">
         <v>24</v>
       </c>
     </row>
@@ -8874,10 +8771,10 @@
       <c r="A111" t="s">
         <v>109</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B111">
         <v>32</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111">
         <v>21</v>
       </c>
     </row>
@@ -9773,7 +9670,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E69E5DE-7812-4896-B0F1-C7271BDE67E5}">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -9829,191 +9726,191 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>320</v>
       </c>
       <c r="B7">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B8">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B11">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B12">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B13">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B14">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B15">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>317</v>
+        <v>250</v>
       </c>
       <c r="B16">
-        <v>85</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="B17">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B19">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B20">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B22">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B23">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B24">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B25">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B26">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B27">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B29">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B30">
         <v>26</v>
@@ -10021,345 +9918,369 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B31">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B32">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B33">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B34">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B35">
-        <v>28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B36">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B38">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B39">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B40">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B41">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B42">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="B43">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B44">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B45">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B46">
-        <v>23</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B47">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B48">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B49">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B50">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B52">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B53">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B54">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B55">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B56">
-        <v>98</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B57">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B58">
-        <v>37</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B59">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B60">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B61">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B62">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B63">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B64">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B65">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B66">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="B67">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B68">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B69">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B70">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B71">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B72">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
+        <v>304</v>
+      </c>
+      <c r="B73">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>305</v>
+      </c>
+      <c r="B74">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>306</v>
+      </c>
+      <c r="B75">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
         <v>307</v>
       </c>
-      <c r="B73">
+      <c r="B76">
         <v>33</v>
       </c>
     </row>

--- a/data_analysis/analysis_selected_solutions.xlsx
+++ b/data_analysis/analysis_selected_solutions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dados\Dafny\TESTDAFNY110\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3729A8-E5A1-46D9-A5AE-A0FFDBED66FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B6EEB2-6D94-4432-BEFF-E0FBA7E4F7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{AD00872A-3429-4154-B9D8-B04F44A65181}"/>
   </bookViews>
@@ -1074,7 +1074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1095,6 +1095,7 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4290,11 +4291,11 @@
       </c>
       <c r="G9">
         <f>IFERROR(VLOOKUP(C9,locs_minimized!A:B,2,0),F9)</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
@@ -4450,11 +4451,11 @@
       </c>
       <c r="G14">
         <f>IFERROR(VLOOKUP(C14,locs_minimized!A:B,2,0),F14)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -4482,11 +4483,11 @@
       </c>
       <c r="G15">
         <f>IFERROR(VLOOKUP(C15,locs_minimized!A:B,2,0),F15)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -4514,11 +4515,11 @@
       </c>
       <c r="G16">
         <f>IFERROR(VLOOKUP(C16,locs_minimized!A:B,2,0),F16)</f>
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="I16">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
@@ -4578,11 +4579,11 @@
       </c>
       <c r="G18">
         <f>IFERROR(VLOOKUP(C18,locs_minimized!A:B,2,0),F18)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I18">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -4610,11 +4611,11 @@
       </c>
       <c r="G19">
         <f>IFERROR(VLOOKUP(C19,locs_minimized!A:B,2,0),F19)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I19">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
@@ -4642,11 +4643,11 @@
       </c>
       <c r="G20">
         <f>IFERROR(VLOOKUP(C20,locs_minimized!A:B,2,0),F20)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
@@ -4674,11 +4675,11 @@
       </c>
       <c r="G21">
         <f>IFERROR(VLOOKUP(C21,locs_minimized!A:B,2,0),F21)</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I21">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
@@ -4898,11 +4899,11 @@
       </c>
       <c r="G28">
         <f>IFERROR(VLOOKUP(C28,locs_minimized!A:B,2,0),F28)</f>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I28">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -5058,11 +5059,11 @@
       </c>
       <c r="G33">
         <f>IFERROR(VLOOKUP(C33,locs_minimized!A:B,2,0),F33)</f>
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I33">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -5250,11 +5251,11 @@
       </c>
       <c r="G39">
         <f>IFERROR(VLOOKUP(C39,locs_minimized!A:B,2,0),F39)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I39">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
@@ -5506,11 +5507,11 @@
       </c>
       <c r="G47">
         <f>IFERROR(VLOOKUP(C47,locs_minimized!A:B,2,0),F47)</f>
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I47">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -5954,11 +5955,11 @@
       </c>
       <c r="G61">
         <f>IFERROR(VLOOKUP(C61,locs_minimized!A:B,2,0),F61)</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I61">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -6114,11 +6115,11 @@
       </c>
       <c r="G66">
         <f>IFERROR(VLOOKUP(C66,locs_minimized!A:B,2,0),F66)</f>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I66">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.45">
@@ -6146,11 +6147,11 @@
       </c>
       <c r="G67">
         <f>IFERROR(VLOOKUP(C67,locs_minimized!A:B,2,0),F67)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I67">
         <f t="shared" ref="I67:I110" si="3">G67-D67</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
@@ -6178,11 +6179,11 @@
       </c>
       <c r="G68">
         <f>IFERROR(VLOOKUP(C68,locs_minimized!A:B,2,0),F68)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I68">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.45">
@@ -6466,11 +6467,11 @@
       </c>
       <c r="G77">
         <f>IFERROR(VLOOKUP(C77,locs_minimized!A:B,2,0),F77)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I77">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.45">
@@ -6690,11 +6691,11 @@
       </c>
       <c r="G84">
         <f>IFERROR(VLOOKUP(C84,locs_minimized!A:B,2,0),F84)</f>
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I84">
         <f t="shared" si="3"/>
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -6882,11 +6883,11 @@
       </c>
       <c r="G90">
         <f>IFERROR(VLOOKUP(C90,locs_minimized!A:B,2,0),F90)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I90">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -7330,11 +7331,11 @@
       </c>
       <c r="G104">
         <f>IFERROR(VLOOKUP(C104,locs_minimized!A:B,2,0),F104)</f>
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="I104">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.45">
@@ -7394,11 +7395,11 @@
       </c>
       <c r="G106">
         <f>IFERROR(VLOOKUP(C106,locs_minimized!A:B,2,0),F106)</f>
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I106">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -7490,11 +7491,11 @@
       </c>
       <c r="G109">
         <f>IFERROR(VLOOKUP(C109,locs_minimized!A:B,2,0),F109)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I109">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
@@ -7515,11 +7516,11 @@
       </c>
       <c r="G110">
         <f t="shared" si="4"/>
-        <v>3809</v>
+        <v>3751</v>
       </c>
       <c r="I110">
         <f t="shared" si="3"/>
-        <v>412</v>
+        <v>354</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -7532,13 +7533,13 @@
       </c>
       <c r="G111" s="5">
         <f>G110/D110-1</f>
-        <v>0.12128348542831913</v>
+        <v>0.10420959670297325</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="G112">
-        <f>(G110-E110)/(F110-E110)</f>
-        <v>0.44090177133655395</v>
+      <c r="G112" s="10">
+        <f>1-(G110-E110)/(F110-E110)</f>
+        <v>0.57777777777777772</v>
       </c>
     </row>
   </sheetData>
@@ -9721,7 +9722,7 @@
         <v>241</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
@@ -9753,7 +9754,7 @@
         <v>244</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
@@ -9761,7 +9762,7 @@
         <v>245</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
@@ -9769,7 +9770,7 @@
         <v>246</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
@@ -9785,7 +9786,7 @@
         <v>248</v>
       </c>
       <c r="B14">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
@@ -9793,7 +9794,7 @@
         <v>249</v>
       </c>
       <c r="B15">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
@@ -9801,7 +9802,7 @@
         <v>250</v>
       </c>
       <c r="B16">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
@@ -9809,7 +9810,7 @@
         <v>317</v>
       </c>
       <c r="B17">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
@@ -9857,7 +9858,7 @@
         <v>256</v>
       </c>
       <c r="B23">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
@@ -9889,7 +9890,7 @@
         <v>260</v>
       </c>
       <c r="B27">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -9905,7 +9906,7 @@
         <v>262</v>
       </c>
       <c r="B29">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
@@ -9953,7 +9954,7 @@
         <v>268</v>
       </c>
       <c r="B35">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -10009,7 +10010,7 @@
         <v>275</v>
       </c>
       <c r="B42">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
@@ -10025,7 +10026,7 @@
         <v>276</v>
       </c>
       <c r="B44">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
@@ -10033,7 +10034,7 @@
         <v>277</v>
       </c>
       <c r="B45">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -10041,7 +10042,7 @@
         <v>278</v>
       </c>
       <c r="B46">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
@@ -10097,7 +10098,7 @@
         <v>285</v>
       </c>
       <c r="B53">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
@@ -10137,7 +10138,7 @@
         <v>290</v>
       </c>
       <c r="B58">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
@@ -10153,7 +10154,7 @@
         <v>292</v>
       </c>
       <c r="B60">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
@@ -10249,7 +10250,7 @@
         <v>303</v>
       </c>
       <c r="B72">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
@@ -10257,7 +10258,7 @@
         <v>304</v>
       </c>
       <c r="B73">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.45">
@@ -10281,7 +10282,7 @@
         <v>307</v>
       </c>
       <c r="B76">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data_analysis/analysis_selected_solutions.xlsx
+++ b/data_analysis/analysis_selected_solutions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dados\Dafny\TESTDAFNY110\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B6EEB2-6D94-4432-BEFF-E0FBA7E4F7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C58C879-4270-471F-9538-4523557D1E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{AD00872A-3429-4154-B9D8-B04F44A65181}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="323">
   <si>
     <t>Filename</t>
   </si>
@@ -5507,11 +5507,11 @@
       </c>
       <c r="G47">
         <f>IFERROR(VLOOKUP(C47,locs_minimized!A:B,2,0),F47)</f>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I47">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -7516,11 +7516,11 @@
       </c>
       <c r="G110">
         <f t="shared" si="4"/>
-        <v>3751</v>
+        <v>3747</v>
       </c>
       <c r="I110">
         <f t="shared" si="3"/>
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -7533,13 +7533,13 @@
       </c>
       <c r="G111" s="5">
         <f>G110/D110-1</f>
-        <v>0.10420959670297325</v>
+        <v>0.10303208713570799</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="G112" s="10">
         <f>1-(G110-E110)/(F110-E110)</f>
-        <v>0.57777777777777772</v>
+        <v>0.57906602254428341</v>
       </c>
     </row>
   </sheetData>
@@ -9671,7 +9671,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E69E5DE-7812-4896-B0F1-C7271BDE67E5}">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -9954,7 +9954,7 @@
         <v>268</v>
       </c>
       <c r="B35">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -10283,6 +10283,270 @@
       </c>
       <c r="B76">
         <v>34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>200</v>
+      </c>
+      <c r="B78">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>202</v>
+      </c>
+      <c r="B79">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>203</v>
+      </c>
+      <c r="B80">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>204</v>
+      </c>
+      <c r="B81">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>201</v>
+      </c>
+      <c r="B83">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>207</v>
+      </c>
+      <c r="B85">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>208</v>
+      </c>
+      <c r="B86">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>209</v>
+      </c>
+      <c r="B87">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>210</v>
+      </c>
+      <c r="B88">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>211</v>
+      </c>
+      <c r="B89">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>213</v>
+      </c>
+      <c r="B91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>217</v>
+      </c>
+      <c r="B95">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>218</v>
+      </c>
+      <c r="B96">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>224</v>
+      </c>
+      <c r="B102">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>226</v>
+      </c>
+      <c r="B103">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>227</v>
+      </c>
+      <c r="B104">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>229</v>
+      </c>
+      <c r="B106">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>225</v>
+      </c>
+      <c r="B108">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>231</v>
+      </c>
+      <c r="B109">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
